--- a/technology_surveys/039_ecommerce_order_management_software_evaluation_checklist--technology_surveys.xlsx
+++ b/technology_surveys/039_ecommerce_order_management_software_evaluation_checklist--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>formheader</t>
+          <t>formheader_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecommerce Order Management Software Evaluation Checklist Form</t>
+          <t>Formheader 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Product Customization</t>
+          <t>Field3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product Customization</t>
+          <t>Field4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ordermanagementoptions</t>
+          <t>Field9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>orderinformation</t>
+          <t>Field13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ordermanagementoptions</t>
+          <t>Field14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>orderinformation</t>
+          <t>Field15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ordernote</t>
+          <t>Field16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>orderinformation</t>
+          <t>Field17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecommerce Order Management Software Evaluation Checklist Form</t>
+          <t>Formfooter</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
